--- a/JsonConverter/ExcelFiles/BaseStage.xlsx
+++ b/JsonConverter/ExcelFiles/BaseStage.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9084A7F0-3959-42FF-87B8-C0BC56272695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28416" yWindow="2304" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2436" yWindow="2652" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseStage" sheetId="1" r:id="rId1"/>
